--- a/Documents/SGE-lang-country-F2H26-Translation Document_Ar V3_final.xlsx
+++ b/Documents/SGE-lang-country-F2H26-Translation Document_Ar V3_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleksandr.k\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Adobe-Form-Builder-main\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1973BB3-61A4-42E8-819D-48D9BD4727E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D705EB-D819-44F1-A80B-4DDCB7B709CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Complete Translations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="217">
   <si>
     <r>
       <rPr>
@@ -764,6 +764,12 @@
   </si>
   <si>
     <t xml:space="preserve">خيار الشراء بغرض التجربة </t>
+  </si>
+  <si>
+    <t>Project Code</t>
+  </si>
+  <si>
+    <t>F2H26</t>
   </si>
 </sst>
 </file>
@@ -1373,16 +1379,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D84"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="63.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.42578125" style="17" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="17"/>
+    <col min="1" max="1" width="34.44140625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="63.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.44140625" style="17" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>46</v>
       </c>
@@ -1396,20 +1402,24 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11"/>
-      <c r="B2"/>
-      <c r="C2" s="12"/>
+      <c r="B2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>216</v>
+      </c>
       <c r="D2" s="12"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="28" t="s">
         <v>51</v>
       </c>
       <c r="C3" s="29"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" t="s">
         <v>39</v>
@@ -1421,7 +1431,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" t="s">
         <v>81</v>
@@ -1433,7 +1443,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
         <v>14</v>
@@ -1446,7 +1456,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" t="s">
         <v>45</v>
@@ -1454,13 +1464,13 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="2" t="s">
         <v>50</v>
@@ -1472,7 +1482,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>70</v>
       </c>
@@ -1484,7 +1494,7 @@
       </c>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" t="s">
         <v>34</v>
@@ -1494,7 +1504,7 @@
       </c>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>62</v>
       </c>
@@ -1506,7 +1516,7 @@
       </c>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>63</v>
       </c>
@@ -1518,7 +1528,7 @@
       </c>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>64</v>
       </c>
@@ -1530,13 +1540,13 @@
       </c>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
     </row>
-    <row r="16" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>71</v>
       </c>
@@ -1548,7 +1558,7 @@
       </c>
       <c r="D16" s="10"/>
     </row>
-    <row r="17" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
       <c r="B17" t="s">
         <v>89</v>
@@ -1558,7 +1568,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>116</v>
       </c>
@@ -1570,7 +1580,7 @@
       </c>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>117</v>
       </c>
@@ -1582,7 +1592,7 @@
       </c>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>118</v>
       </c>
@@ -1594,7 +1604,7 @@
       </c>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>65</v>
       </c>
@@ -1606,7 +1616,7 @@
       </c>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>66</v>
       </c>
@@ -1618,7 +1628,7 @@
       </c>
       <c r="D22" s="9"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>67</v>
       </c>
@@ -1630,7 +1640,7 @@
       </c>
       <c r="D23" s="9"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>68</v>
       </c>
@@ -1642,7 +1652,7 @@
       </c>
       <c r="D24" s="9"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>69</v>
       </c>
@@ -1654,13 +1664,13 @@
       </c>
       <c r="D25" s="9"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
     </row>
-    <row r="27" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>72</v>
       </c>
@@ -1672,7 +1682,7 @@
       </c>
       <c r="D27" s="10"/>
     </row>
-    <row r="28" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" t="s">
         <v>38</v>
@@ -1682,7 +1692,7 @@
       </c>
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>119</v>
       </c>
@@ -1694,7 +1704,7 @@
       </c>
       <c r="D29" s="9"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>120</v>
       </c>
@@ -1706,7 +1716,7 @@
       </c>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>121</v>
       </c>
@@ -1718,7 +1728,7 @@
       </c>
       <c r="D31" s="9"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>122</v>
       </c>
@@ -1730,7 +1740,7 @@
       </c>
       <c r="D32" s="9"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>123</v>
       </c>
@@ -1742,13 +1752,13 @@
       </c>
       <c r="D33" s="9"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34"/>
       <c r="C34" s="19"/>
       <c r="D34" s="9"/>
     </row>
-    <row r="35" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>73</v>
       </c>
@@ -1760,7 +1770,7 @@
       </c>
       <c r="D35" s="10"/>
     </row>
-    <row r="36" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" t="s">
         <v>80</v>
@@ -1770,7 +1780,7 @@
       </c>
       <c r="D36" s="10"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>124</v>
       </c>
@@ -1782,7 +1792,7 @@
       </c>
       <c r="D37" s="9"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>125</v>
       </c>
@@ -1794,7 +1804,7 @@
       </c>
       <c r="D38" s="9"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>126</v>
       </c>
@@ -1806,7 +1816,7 @@
       </c>
       <c r="D39" s="9"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>127</v>
       </c>
@@ -1818,7 +1828,7 @@
       </c>
       <c r="D40" s="9"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>128</v>
       </c>
@@ -1830,7 +1840,7 @@
       </c>
       <c r="D41" s="9"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>129</v>
       </c>
@@ -1842,13 +1852,13 @@
       </c>
       <c r="D42" s="9"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43"/>
       <c r="C43"/>
       <c r="D43"/>
     </row>
-    <row r="44" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>74</v>
       </c>
@@ -1860,7 +1870,7 @@
       </c>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>62</v>
       </c>
@@ -1872,7 +1882,7 @@
       </c>
       <c r="D45" s="10"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>63</v>
       </c>
@@ -1884,7 +1894,7 @@
       </c>
       <c r="D46" s="9"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>64</v>
       </c>
@@ -1896,7 +1906,7 @@
       </c>
       <c r="D47" s="9"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>65</v>
       </c>
@@ -1908,13 +1918,13 @@
       </c>
       <c r="D48" s="9"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49"/>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>75</v>
       </c>
@@ -1922,13 +1932,13 @@
       <c r="C50"/>
       <c r="D50" s="1"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51"/>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
         <v>130</v>
       </c>
@@ -1936,7 +1946,7 @@
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>131</v>
       </c>
@@ -1944,19 +1954,19 @@
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54"/>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
     </row>
-    <row r="55" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55"/>
       <c r="C55"/>
       <c r="D55"/>
     </row>
-    <row r="56" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="2" t="s">
         <v>49</v>
@@ -1966,7 +1976,7 @@
       </c>
       <c r="D56" s="8"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>1</v>
       </c>
@@ -1978,7 +1988,7 @@
       </c>
       <c r="D57" s="9"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>3</v>
       </c>
@@ -1990,7 +2000,7 @@
       </c>
       <c r="D58" s="9"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>6</v>
       </c>
@@ -2002,7 +2012,7 @@
       </c>
       <c r="D59" s="9"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>5</v>
       </c>
@@ -2014,13 +2024,13 @@
       </c>
       <c r="D60" s="9"/>
     </row>
-    <row r="61" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61"/>
       <c r="C61"/>
       <c r="D61"/>
     </row>
-    <row r="62" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="2" t="s">
         <v>48</v>
@@ -2032,7 +2042,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>8</v>
       </c>
@@ -2044,7 +2054,7 @@
       </c>
       <c r="D63" s="9"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
         <v>10</v>
       </c>
@@ -2056,7 +2066,7 @@
       </c>
       <c r="D64" s="9"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
         <v>12</v>
       </c>
@@ -2068,7 +2078,7 @@
       </c>
       <c r="D65" s="9"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>13</v>
       </c>
@@ -2080,7 +2090,7 @@
       </c>
       <c r="D66" s="9"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>15</v>
       </c>
@@ -2092,7 +2102,7 @@
       </c>
       <c r="D67" s="9"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>17</v>
       </c>
@@ -2104,7 +2114,7 @@
       </c>
       <c r="D68" s="9"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>18</v>
       </c>
@@ -2116,7 +2126,7 @@
       </c>
       <c r="D69" s="9"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>23</v>
       </c>
@@ -2128,7 +2138,7 @@
       </c>
       <c r="D70" s="9"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>19</v>
       </c>
@@ -2140,7 +2150,7 @@
       </c>
       <c r="D71" s="9"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>110</v>
       </c>
@@ -2152,7 +2162,7 @@
       </c>
       <c r="D72" s="9"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>24</v>
       </c>
@@ -2166,7 +2176,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>111</v>
       </c>
@@ -2178,7 +2188,7 @@
       </c>
       <c r="D74" s="9"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>25</v>
       </c>
@@ -2190,7 +2200,7 @@
       </c>
       <c r="D75" s="9"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>105</v>
       </c>
@@ -2202,13 +2212,13 @@
       </c>
       <c r="D76" s="9"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77"/>
       <c r="C77" s="19"/>
       <c r="D77" s="9"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>59</v>
       </c>
@@ -2216,7 +2226,7 @@
       <c r="C78"/>
       <c r="D78"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>134</v>
       </c>
@@ -2228,7 +2238,7 @@
       </c>
       <c r="D79" s="9"/>
     </row>
-    <row r="80" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>135</v>
       </c>
@@ -2240,7 +2250,7 @@
       </c>
       <c r="D80" s="9"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>136</v>
       </c>
@@ -2254,7 +2264,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>137</v>
       </c>
@@ -2266,7 +2276,7 @@
       </c>
       <c r="D82" s="9"/>
     </row>
-    <row r="83" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5"/>
       <c r="B83" s="2" t="s">
         <v>112</v>
@@ -2274,7 +2284,7 @@
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>28</v>
       </c>
@@ -2328,7 +2338,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A64C1A-A47F-4966-A6AE-94C67F107E67}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2338,12 +2348,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>138</v>
       </c>
@@ -2351,7 +2361,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -2362,7 +2372,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -2373,7 +2383,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -2384,7 +2394,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -2395,7 +2405,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>57</v>
       </c>
@@ -2403,7 +2413,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>55</v>
       </c>
@@ -2411,7 +2421,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>53</v>
       </c>
